--- a/data.xlsx
+++ b/data.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\python work\school_management_by_sumayya\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F30FD7D3-7FAF-4A51-B908-223B015F361D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755" activeTab="3"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GradeIII" sheetId="1" r:id="rId1"/>
@@ -17,10 +18,24 @@
     <sheet name="GradeV" sheetId="3" r:id="rId3"/>
     <sheet name="GradeVI" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -116,39 +131,6 @@
     <t>GR_009</t>
   </si>
   <si>
-    <t>GR_010</t>
-  </si>
-  <si>
-    <t>GR_011</t>
-  </si>
-  <si>
-    <t>GR_012</t>
-  </si>
-  <si>
-    <t>GR_013</t>
-  </si>
-  <si>
-    <t>GR_014</t>
-  </si>
-  <si>
-    <t>GR_015</t>
-  </si>
-  <si>
-    <t>GR_016</t>
-  </si>
-  <si>
-    <t>GR_017</t>
-  </si>
-  <si>
-    <t>GR_018</t>
-  </si>
-  <si>
-    <t>GR_019</t>
-  </si>
-  <si>
-    <t>GR_020</t>
-  </si>
-  <si>
     <t>Sumayya</t>
   </si>
   <si>
@@ -729,13 +711,46 @@
   </si>
   <si>
     <t>Hashmi Zaheer</t>
+  </si>
+  <si>
+    <t>GR_0010</t>
+  </si>
+  <si>
+    <t>GR_0011</t>
+  </si>
+  <si>
+    <t>GR_0012</t>
+  </si>
+  <si>
+    <t>GR_0013</t>
+  </si>
+  <si>
+    <t>GR_0014</t>
+  </si>
+  <si>
+    <t>GR_0015</t>
+  </si>
+  <si>
+    <t>GR_0016</t>
+  </si>
+  <si>
+    <t>GR_0017</t>
+  </si>
+  <si>
+    <t>GR_0018</t>
+  </si>
+  <si>
+    <t>GR_0019</t>
+  </si>
+  <si>
+    <t>GR_0020</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -754,6 +769,12 @@
       <b/>
       <sz val="12"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -958,7 +979,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="TextBox 1"/>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1036,7 +1063,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="Oval 3"/>
+        <xdr:cNvPr id="4" name="Oval 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1131,7 +1164,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="TextBox 1"/>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1209,7 +1248,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="Oval 2"/>
+        <xdr:cNvPr id="3" name="Oval 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1304,7 +1349,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="TextBox 1"/>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1382,7 +1433,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="Oval 2"/>
+        <xdr:cNvPr id="3" name="Oval 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1477,7 +1534,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="TextBox 1"/>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1555,7 +1618,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="Oval 2"/>
+        <xdr:cNvPr id="3" name="Oval 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1895,7 +1964,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor theme="8" tint="-0.499984740745262"/>
   </sheetPr>
@@ -1981,13 +2050,13 @@
         <v>20</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E8" s="8" t="str">
         <f>IF(D8="Female","A","B")</f>
@@ -2031,7 +2100,7 @@
         <v>15</v>
       </c>
       <c r="R8" s="6" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -2039,10 +2108,10 @@
         <v>21</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>14</v>
@@ -2089,7 +2158,7 @@
         <v>15</v>
       </c>
       <c r="R9" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -2097,13 +2166,13 @@
         <v>22</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E10" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2147,7 +2216,7 @@
         <v>15</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -2155,13 +2224,13 @@
         <v>23</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E11" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2205,7 +2274,7 @@
         <v>15</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -2213,10 +2282,10 @@
         <v>24</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>14</v>
@@ -2263,7 +2332,7 @@
         <v>15</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -2271,13 +2340,13 @@
         <v>25</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E13" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2321,7 +2390,7 @@
         <v>15</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -2329,10 +2398,10 @@
         <v>26</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>14</v>
@@ -2379,7 +2448,7 @@
         <v>15</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -2387,10 +2456,10 @@
         <v>27</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>14</v>
@@ -2437,7 +2506,7 @@
         <v>15</v>
       </c>
       <c r="R15" s="4" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -2445,10 +2514,10 @@
         <v>28</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>14</v>
@@ -2495,21 +2564,21 @@
         <v>15</v>
       </c>
       <c r="R16" s="4" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>29</v>
+        <v>223</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E17" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2553,21 +2622,21 @@
         <v>15</v>
       </c>
       <c r="R17" s="4" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>30</v>
+        <v>224</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E18" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2608,24 +2677,24 @@
         <v>0.9</v>
       </c>
       <c r="Q18" s="4" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="R18" s="4" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>42</v>
       </c>
       <c r="E19" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2666,21 +2735,21 @@
         <v>0.9</v>
       </c>
       <c r="Q19" s="4" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="R19" s="4" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>32</v>
+        <v>226</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>14</v>
@@ -2724,21 +2793,21 @@
         <v>0.9</v>
       </c>
       <c r="Q20" s="4" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="R20" s="4" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>33</v>
+        <v>227</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>14</v>
@@ -2782,21 +2851,21 @@
         <v>0.9</v>
       </c>
       <c r="Q21" s="4" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="R21" s="4" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>34</v>
+        <v>228</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>14</v>
@@ -2840,21 +2909,21 @@
         <v>0.9</v>
       </c>
       <c r="Q22" s="4" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="R22" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>35</v>
+        <v>229</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>14</v>
@@ -2898,21 +2967,21 @@
         <v>0.9</v>
       </c>
       <c r="Q23" s="4" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="R23" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>36</v>
+        <v>230</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>14</v>
@@ -2959,18 +3028,18 @@
         <v>15</v>
       </c>
       <c r="R24" s="4" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="25" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>37</v>
+        <v>231</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>14</v>
@@ -3017,21 +3086,21 @@
         <v>15</v>
       </c>
       <c r="R25" s="4" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>38</v>
+        <v>232</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E26" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3075,18 +3144,18 @@
         <v>15</v>
       </c>
       <c r="R26" s="4" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>39</v>
+        <v>233</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>14</v>
@@ -3133,10 +3202,11 @@
         <v>15</v>
       </c>
       <c r="R27" s="4" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <drawing r:id="rId2"/>
@@ -3144,7 +3214,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor theme="5" tint="-0.249977111117893"/>
   </sheetPr>
@@ -3219,16 +3289,16 @@
     </row>
     <row r="8" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E8" s="8" t="str">
         <f>IF(D8="Female","A","B")</f>
@@ -3272,21 +3342,21 @@
         <v>15</v>
       </c>
       <c r="R8" s="6" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E9" s="2" t="str">
         <f t="shared" ref="E9:E27" si="0">IF(D9="Female","A","B")</f>
@@ -3330,18 +3400,18 @@
         <v>15</v>
       </c>
       <c r="R9" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>14</v>
@@ -3388,18 +3458,18 @@
         <v>15</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>14</v>
@@ -3446,18 +3516,18 @@
         <v>15</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>14</v>
@@ -3504,21 +3574,21 @@
         <v>15</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E13" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3559,24 +3629,24 @@
         <v>0.8</v>
       </c>
       <c r="Q13" s="4" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E14" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3617,21 +3687,21 @@
         <v>0.89</v>
       </c>
       <c r="Q14" s="4" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>14</v>
@@ -3675,24 +3745,24 @@
         <v>0.61</v>
       </c>
       <c r="Q15" s="4" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="R15" s="4" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E16" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3733,24 +3803,24 @@
         <v>0.63</v>
       </c>
       <c r="Q16" s="4" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="R16" s="4" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E17" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3791,24 +3861,24 @@
         <v>0.48</v>
       </c>
       <c r="Q17" s="4" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="R17" s="4" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E18" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3849,24 +3919,24 @@
         <v>0.59</v>
       </c>
       <c r="Q18" s="4" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="R18" s="4" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E19" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3907,24 +3977,24 @@
         <v>0.45</v>
       </c>
       <c r="Q19" s="4" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="R19" s="4" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E20" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3965,24 +4035,24 @@
         <v>0.75</v>
       </c>
       <c r="Q20" s="4" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="R20" s="4" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E21" s="2" t="str">
         <f t="shared" si="0"/>
@@ -4023,24 +4093,24 @@
         <v>0.72</v>
       </c>
       <c r="Q21" s="4" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="R21" s="4" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E22" s="2" t="str">
         <f t="shared" si="0"/>
@@ -4081,21 +4151,21 @@
         <v>0.68</v>
       </c>
       <c r="Q22" s="4" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="R22" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>14</v>
@@ -4139,24 +4209,24 @@
         <v>0.49</v>
       </c>
       <c r="Q23" s="4" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="R23" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E24" s="2" t="str">
         <f t="shared" si="0"/>
@@ -4200,21 +4270,21 @@
         <v>15</v>
       </c>
       <c r="R24" s="4" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="25" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E25" s="2" t="str">
         <f t="shared" si="0"/>
@@ -4258,18 +4328,18 @@
         <v>15</v>
       </c>
       <c r="R25" s="4" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>14</v>
@@ -4316,18 +4386,18 @@
         <v>15</v>
       </c>
       <c r="R26" s="4" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>14</v>
@@ -4374,7 +4444,7 @@
         <v>15</v>
       </c>
       <c r="R27" s="4" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -4384,7 +4454,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor theme="7" tint="0.39997558519241921"/>
   </sheetPr>
@@ -4468,16 +4538,16 @@
     </row>
     <row r="8" spans="1:18" s="15" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E8" s="8" t="str">
         <f>IF(D8="Female","A","B")</f>
@@ -4485,19 +4555,19 @@
       </c>
       <c r="F8" s="16">
         <f ca="1">RANDBETWEEN(40,100)</f>
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G8" s="16">
         <f t="shared" ref="G8:M23" ca="1" si="0">RANDBETWEEN(40,100)</f>
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="H8" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="I8" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="J8" s="16">
         <f t="shared" ca="1" si="0"/>
@@ -4505,19 +4575,19 @@
       </c>
       <c r="K8" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="L8" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="M8" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="N8" s="7">
         <f ca="1">SUM(F8:M8)</f>
-        <v>544</v>
+        <v>594</v>
       </c>
       <c r="O8" s="7">
         <v>800</v>
@@ -4529,21 +4599,21 @@
         <v>15</v>
       </c>
       <c r="R8" s="6" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:18" s="15" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E9" s="2" t="str">
         <f t="shared" ref="E9:E27" si="1">IF(D9="Female","A","B")</f>
@@ -4551,39 +4621,39 @@
       </c>
       <c r="F9" s="14">
         <f t="shared" ref="F9:M27" ca="1" si="2">RANDBETWEEN(40,100)</f>
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="G9" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H9" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="I9" s="14">
         <f t="shared" ca="1" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="J9" s="14">
+        <f t="shared" ca="1" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="K9" s="14">
+        <f t="shared" ca="1" si="0"/>
+        <v>49</v>
+      </c>
+      <c r="L9" s="14">
+        <f t="shared" ca="1" si="0"/>
+        <v>62</v>
+      </c>
+      <c r="M9" s="14">
+        <f t="shared" ca="1" si="0"/>
         <v>87</v>
-      </c>
-      <c r="J9" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>77</v>
-      </c>
-      <c r="K9" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>64</v>
-      </c>
-      <c r="L9" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>73</v>
-      </c>
-      <c r="M9" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>74</v>
       </c>
       <c r="N9" s="1">
         <f t="shared" ref="N9:N27" ca="1" si="3">SUM(F9:M9)</f>
-        <v>606</v>
+        <v>519</v>
       </c>
       <c r="O9" s="1">
         <v>800</v>
@@ -4595,18 +4665,18 @@
         <v>15</v>
       </c>
       <c r="R9" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:18" s="15" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>14</v>
@@ -4617,39 +4687,39 @@
       </c>
       <c r="F10" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G10" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="H10" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="I10" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J10" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="K10" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="L10" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="M10" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>98</v>
+        <v>41</v>
       </c>
       <c r="N10" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>596</v>
+        <v>555</v>
       </c>
       <c r="O10" s="1">
         <v>800</v>
@@ -4661,18 +4731,18 @@
         <v>15</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:18" s="15" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>14</v>
@@ -4683,23 +4753,23 @@
       </c>
       <c r="F11" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="G11" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="H11" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="I11" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="J11" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="K11" s="14">
         <f t="shared" ca="1" si="0"/>
@@ -4707,15 +4777,15 @@
       </c>
       <c r="L11" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="M11" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="N11" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>473</v>
+        <v>492</v>
       </c>
       <c r="O11" s="1">
         <v>800</v>
@@ -4727,21 +4797,21 @@
         <v>15</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:18" s="15" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E12" s="2" t="str">
         <f t="shared" si="1"/>
@@ -4749,39 +4819,39 @@
       </c>
       <c r="F12" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>96</v>
+        <v>51</v>
       </c>
       <c r="G12" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="H12" s="14">
         <f t="shared" ca="1" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="I12" s="14">
+        <f t="shared" ca="1" si="0"/>
         <v>88</v>
       </c>
-      <c r="I12" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>57</v>
-      </c>
       <c r="J12" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="K12" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="L12" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="M12" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="N12" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>608</v>
+        <v>580</v>
       </c>
       <c r="O12" s="1">
         <v>800</v>
@@ -4793,21 +4863,21 @@
         <v>15</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:18" s="15" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E13" s="2" t="str">
         <f t="shared" si="1"/>
@@ -4815,39 +4885,39 @@
       </c>
       <c r="F13" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G13" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>99</v>
+        <v>58</v>
       </c>
       <c r="H13" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>46</v>
+        <v>93</v>
       </c>
       <c r="I13" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>82</v>
+        <v>43</v>
       </c>
       <c r="J13" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>84</v>
+        <v>47</v>
       </c>
       <c r="K13" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>88</v>
+        <v>40</v>
       </c>
       <c r="L13" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="M13" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="N13" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>643</v>
+        <v>476</v>
       </c>
       <c r="O13" s="1">
         <v>800</v>
@@ -4856,24 +4926,24 @@
         <v>0.8</v>
       </c>
       <c r="Q13" s="4" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:18" s="15" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E14" s="2" t="str">
         <f t="shared" si="1"/>
@@ -4881,39 +4951,39 @@
       </c>
       <c r="F14" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="G14" s="14">
         <f t="shared" ca="1" si="0"/>
+        <v>66</v>
+      </c>
+      <c r="H14" s="14">
+        <f t="shared" ca="1" si="0"/>
+        <v>81</v>
+      </c>
+      <c r="I14" s="14">
+        <f t="shared" ca="1" si="0"/>
+        <v>52</v>
+      </c>
+      <c r="J14" s="14">
+        <f t="shared" ca="1" si="0"/>
         <v>60</v>
       </c>
-      <c r="H14" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>69</v>
-      </c>
-      <c r="I14" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>98</v>
-      </c>
-      <c r="J14" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>94</v>
-      </c>
       <c r="K14" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>97</v>
+        <v>42</v>
       </c>
       <c r="L14" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>43</v>
+        <v>90</v>
       </c>
       <c r="M14" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="N14" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>620</v>
+        <v>555</v>
       </c>
       <c r="O14" s="1">
         <v>800</v>
@@ -4922,24 +4992,24 @@
         <v>0.89</v>
       </c>
       <c r="Q14" s="4" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:18" s="15" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E15" s="2" t="str">
         <f t="shared" si="1"/>
@@ -4947,39 +5017,39 @@
       </c>
       <c r="F15" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>52</v>
+        <v>98</v>
       </c>
       <c r="G15" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="H15" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="I15" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="J15" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="K15" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="L15" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="M15" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="N15" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>484</v>
+        <v>571</v>
       </c>
       <c r="O15" s="1">
         <v>800</v>
@@ -4988,24 +5058,24 @@
         <v>0.61</v>
       </c>
       <c r="Q15" s="4" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="R15" s="4" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:18" s="15" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E16" s="2" t="str">
         <f t="shared" si="1"/>
@@ -5013,39 +5083,39 @@
       </c>
       <c r="F16" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>93</v>
+        <v>67</v>
       </c>
       <c r="G16" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>58</v>
+        <v>97</v>
       </c>
       <c r="H16" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="I16" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>85</v>
+        <v>47</v>
       </c>
       <c r="J16" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>49</v>
+        <v>97</v>
       </c>
       <c r="K16" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="L16" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="M16" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="N16" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>630</v>
+        <v>603</v>
       </c>
       <c r="O16" s="1">
         <v>800</v>
@@ -5054,24 +5124,24 @@
         <v>0.63</v>
       </c>
       <c r="Q16" s="4" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="R16" s="4" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:18" s="15" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E17" s="2" t="str">
         <f t="shared" si="1"/>
@@ -5079,39 +5149,39 @@
       </c>
       <c r="F17" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="G17" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>78</v>
+        <v>42</v>
       </c>
       <c r="H17" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="I17" s="14">
         <f t="shared" ca="1" si="0"/>
+        <v>84</v>
+      </c>
+      <c r="J17" s="14">
+        <f t="shared" ca="1" si="0"/>
+        <v>64</v>
+      </c>
+      <c r="K17" s="14">
+        <f t="shared" ca="1" si="0"/>
+        <v>66</v>
+      </c>
+      <c r="L17" s="14">
+        <f t="shared" ca="1" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="M17" s="14">
+        <f t="shared" ca="1" si="0"/>
         <v>57</v>
-      </c>
-      <c r="J17" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>88</v>
-      </c>
-      <c r="K17" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>93</v>
-      </c>
-      <c r="L17" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>60</v>
-      </c>
-      <c r="M17" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>67</v>
       </c>
       <c r="N17" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>537</v>
+        <v>484</v>
       </c>
       <c r="O17" s="1">
         <v>800</v>
@@ -5120,24 +5190,24 @@
         <v>0.48</v>
       </c>
       <c r="Q17" s="4" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="R17" s="4" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:18" s="15" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E18" s="2" t="str">
         <f t="shared" si="1"/>
@@ -5145,39 +5215,39 @@
       </c>
       <c r="F18" s="14">
         <f t="shared" ca="1" si="2"/>
+        <v>95</v>
+      </c>
+      <c r="G18" s="14">
+        <f t="shared" ca="1" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="H18" s="14">
+        <f t="shared" ca="1" si="0"/>
+        <v>54</v>
+      </c>
+      <c r="I18" s="14">
+        <f t="shared" ca="1" si="0"/>
         <v>93</v>
       </c>
-      <c r="G18" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>94</v>
-      </c>
-      <c r="H18" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>73</v>
-      </c>
-      <c r="I18" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>68</v>
-      </c>
       <c r="J18" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="K18" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="L18" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="M18" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="N18" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>619</v>
+        <v>554</v>
       </c>
       <c r="O18" s="1">
         <v>800</v>
@@ -5186,24 +5256,24 @@
         <v>0.59</v>
       </c>
       <c r="Q18" s="4" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="R18" s="4" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:18" s="15" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E19" s="2" t="str">
         <f t="shared" si="1"/>
@@ -5211,39 +5281,39 @@
       </c>
       <c r="F19" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="G19" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="H19" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="I19" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>51</v>
+        <v>97</v>
       </c>
       <c r="J19" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="K19" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>95</v>
+        <v>52</v>
       </c>
       <c r="L19" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="M19" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N19" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>597</v>
+        <v>610</v>
       </c>
       <c r="O19" s="1">
         <v>800</v>
@@ -5252,24 +5322,24 @@
         <v>0.45</v>
       </c>
       <c r="Q19" s="4" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="R19" s="4" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20" spans="1:18" s="15" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E20" s="2" t="str">
         <f t="shared" si="1"/>
@@ -5277,19 +5347,19 @@
       </c>
       <c r="F20" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="G20" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>42</v>
+        <v>99</v>
       </c>
       <c r="H20" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="I20" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="J20" s="14">
         <f t="shared" ca="1" si="0"/>
@@ -5297,19 +5367,19 @@
       </c>
       <c r="K20" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="L20" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="M20" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="N20" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>440</v>
+        <v>614</v>
       </c>
       <c r="O20" s="1">
         <v>800</v>
@@ -5318,24 +5388,24 @@
         <v>0.75</v>
       </c>
       <c r="Q20" s="4" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="R20" s="4" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:18" s="15" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E21" s="2" t="str">
         <f t="shared" si="1"/>
@@ -5343,39 +5413,39 @@
       </c>
       <c r="F21" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>51</v>
+        <v>97</v>
       </c>
       <c r="G21" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="H21" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="I21" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="J21" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="K21" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="L21" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>86</v>
+        <v>41</v>
       </c>
       <c r="M21" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="N21" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>474</v>
+        <v>523</v>
       </c>
       <c r="O21" s="1">
         <v>800</v>
@@ -5384,21 +5454,21 @@
         <v>0.72</v>
       </c>
       <c r="Q21" s="4" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="R21" s="4" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:18" s="15" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>14</v>
@@ -5409,39 +5479,39 @@
       </c>
       <c r="F22" s="14">
         <f t="shared" ca="1" si="2"/>
+        <v>57</v>
+      </c>
+      <c r="G22" s="14">
+        <f t="shared" ca="1" si="0"/>
+        <v>66</v>
+      </c>
+      <c r="H22" s="14">
+        <f t="shared" ca="1" si="0"/>
+        <v>86</v>
+      </c>
+      <c r="I22" s="14">
+        <f t="shared" ca="1" si="0"/>
+        <v>68</v>
+      </c>
+      <c r="J22" s="14">
+        <f t="shared" ca="1" si="0"/>
         <v>76</v>
       </c>
-      <c r="G22" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>66</v>
-      </c>
-      <c r="H22" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>97</v>
-      </c>
-      <c r="I22" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>79</v>
-      </c>
-      <c r="J22" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>61</v>
-      </c>
       <c r="K22" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>57</v>
+        <v>90</v>
       </c>
       <c r="L22" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="M22" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="N22" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>557</v>
+        <v>588</v>
       </c>
       <c r="O22" s="1">
         <v>800</v>
@@ -5450,21 +5520,21 @@
         <v>0.68</v>
       </c>
       <c r="Q22" s="4" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="R22" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:18" s="15" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>14</v>
@@ -5475,39 +5545,39 @@
       </c>
       <c r="F23" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="G23" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="H23" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I23" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="J23" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="K23" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="L23" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="M23" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="N23" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>619</v>
+        <v>530</v>
       </c>
       <c r="O23" s="1">
         <v>800</v>
@@ -5516,21 +5586,21 @@
         <v>0.49</v>
       </c>
       <c r="Q23" s="4" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="R23" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:18" s="15" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>14</v>
@@ -5541,39 +5611,39 @@
       </c>
       <c r="F24" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G24" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="H24" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="I24" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>93</v>
+        <v>40</v>
       </c>
       <c r="J24" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="K24" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="L24" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="M24" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="N24" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>585</v>
+        <v>543</v>
       </c>
       <c r="O24" s="1">
         <v>800</v>
@@ -5585,18 +5655,18 @@
         <v>15</v>
       </c>
       <c r="R24" s="4" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="25" spans="1:18" s="15" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>14</v>
@@ -5611,35 +5681,35 @@
       </c>
       <c r="G25" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="H25" s="14">
         <f t="shared" ca="1" si="2"/>
+        <v>54</v>
+      </c>
+      <c r="I25" s="14">
+        <f t="shared" ca="1" si="2"/>
         <v>47</v>
       </c>
-      <c r="I25" s="14">
-        <f t="shared" ca="1" si="2"/>
-        <v>51</v>
-      </c>
       <c r="J25" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="K25" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>92</v>
+        <v>49</v>
       </c>
       <c r="L25" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="M25" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N25" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>466</v>
+        <v>441</v>
       </c>
       <c r="O25" s="1">
         <v>800</v>
@@ -5651,18 +5721,18 @@
         <v>15</v>
       </c>
       <c r="R25" s="4" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26" spans="1:18" s="15" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>14</v>
@@ -5673,39 +5743,39 @@
       </c>
       <c r="F26" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G26" s="14">
         <f t="shared" ca="1" si="2"/>
+        <v>45</v>
+      </c>
+      <c r="H26" s="14">
+        <f t="shared" ca="1" si="2"/>
+        <v>83</v>
+      </c>
+      <c r="I26" s="14">
+        <f t="shared" ca="1" si="2"/>
         <v>65</v>
       </c>
-      <c r="H26" s="14">
-        <f t="shared" ca="1" si="2"/>
-        <v>90</v>
-      </c>
-      <c r="I26" s="14">
-        <f t="shared" ca="1" si="2"/>
-        <v>95</v>
-      </c>
       <c r="J26" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="K26" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="L26" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="M26" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="N26" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>566</v>
+        <v>530</v>
       </c>
       <c r="O26" s="1">
         <v>800</v>
@@ -5717,21 +5787,21 @@
         <v>15</v>
       </c>
       <c r="R26" s="4" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27" spans="1:18" s="15" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E27" s="2" t="str">
         <f t="shared" si="1"/>
@@ -5739,39 +5809,39 @@
       </c>
       <c r="F27" s="14">
         <f t="shared" ca="1" si="2"/>
+        <v>77</v>
+      </c>
+      <c r="G27" s="14">
+        <f t="shared" ca="1" si="2"/>
+        <v>42</v>
+      </c>
+      <c r="H27" s="14">
+        <f t="shared" ca="1" si="2"/>
+        <v>47</v>
+      </c>
+      <c r="I27" s="14">
+        <f t="shared" ca="1" si="2"/>
         <v>68</v>
       </c>
-      <c r="G27" s="14">
-        <f t="shared" ca="1" si="2"/>
-        <v>45</v>
-      </c>
-      <c r="H27" s="14">
-        <f t="shared" ca="1" si="2"/>
-        <v>87</v>
-      </c>
-      <c r="I27" s="14">
-        <f t="shared" ca="1" si="2"/>
-        <v>74</v>
-      </c>
       <c r="J27" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="K27" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="L27" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="M27" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="N27" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>534</v>
+        <v>496</v>
       </c>
       <c r="O27" s="1">
         <v>800</v>
@@ -5783,7 +5853,7 @@
         <v>15</v>
       </c>
       <c r="R27" s="4" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -5793,7 +5863,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <tabColor theme="9"/>
   </sheetPr>
@@ -5867,13 +5937,13 @@
     </row>
     <row r="8" spans="1:18" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>14</v>
@@ -5884,39 +5954,39 @@
       </c>
       <c r="F8" s="14">
         <f ca="1">RANDBETWEEN(40,100)</f>
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="G8" s="14">
         <f t="shared" ref="G8:M23" ca="1" si="0">RANDBETWEEN(40,100)</f>
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="H8" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="I8" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="J8" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="K8" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="L8" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>99</v>
+        <v>54</v>
       </c>
       <c r="M8" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="N8" s="1">
         <f ca="1">SUM(F8:M8)</f>
-        <v>640</v>
+        <v>515</v>
       </c>
       <c r="O8" s="1">
         <v>800</v>
@@ -5928,18 +5998,18 @@
         <v>15</v>
       </c>
       <c r="R8" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:18" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>14</v>
@@ -5950,39 +6020,39 @@
       </c>
       <c r="F9" s="14">
         <f t="shared" ref="F9:M27" ca="1" si="2">RANDBETWEEN(40,100)</f>
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G9" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="H9" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I9" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="J9" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K9" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>99</v>
+        <v>64</v>
       </c>
       <c r="L9" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="M9" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="N9" s="1">
         <f t="shared" ref="N9:N27" ca="1" si="3">SUM(F9:M9)</f>
-        <v>580</v>
+        <v>561</v>
       </c>
       <c r="O9" s="1">
         <v>800</v>
@@ -5994,18 +6064,18 @@
         <v>15</v>
       </c>
       <c r="R9" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:18" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>14</v>
@@ -6016,39 +6086,39 @@
       </c>
       <c r="F10" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="G10" s="14">
         <f t="shared" ca="1" si="0"/>
+        <v>55</v>
+      </c>
+      <c r="H10" s="14">
+        <f t="shared" ca="1" si="0"/>
+        <v>91</v>
+      </c>
+      <c r="I10" s="14">
+        <f t="shared" ca="1" si="0"/>
+        <v>55</v>
+      </c>
+      <c r="J10" s="14">
+        <f t="shared" ca="1" si="0"/>
+        <v>96</v>
+      </c>
+      <c r="K10" s="14">
+        <f t="shared" ca="1" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="L10" s="14">
+        <f t="shared" ca="1" si="0"/>
+        <v>93</v>
+      </c>
+      <c r="M10" s="14">
+        <f t="shared" ca="1" si="0"/>
         <v>62</v>
-      </c>
-      <c r="H10" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="I10" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>87</v>
-      </c>
-      <c r="J10" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>44</v>
-      </c>
-      <c r="K10" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>98</v>
-      </c>
-      <c r="L10" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="M10" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>97</v>
       </c>
       <c r="N10" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>536</v>
+        <v>568</v>
       </c>
       <c r="O10" s="1">
         <v>800</v>
@@ -6060,18 +6130,18 @@
         <v>15</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:18" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>14</v>
@@ -6082,39 +6152,39 @@
       </c>
       <c r="F11" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="G11" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="H11" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="I11" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="J11" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="K11" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>98</v>
+        <v>59</v>
       </c>
       <c r="L11" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="M11" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="N11" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>607</v>
+        <v>618</v>
       </c>
       <c r="O11" s="1">
         <v>800</v>
@@ -6126,18 +6196,18 @@
         <v>15</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:18" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>14</v>
@@ -6148,39 +6218,39 @@
       </c>
       <c r="F12" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>50</v>
+        <v>89</v>
       </c>
       <c r="G12" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>43</v>
+        <v>98</v>
       </c>
       <c r="H12" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="I12" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>84</v>
+        <v>44</v>
       </c>
       <c r="J12" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>49</v>
+        <v>93</v>
       </c>
       <c r="K12" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L12" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="M12" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="N12" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>513</v>
+        <v>599</v>
       </c>
       <c r="O12" s="1">
         <v>800</v>
@@ -6192,18 +6262,18 @@
         <v>15</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:18" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>14</v>
@@ -6214,39 +6284,39 @@
       </c>
       <c r="F13" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="G13" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="H13" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="I13" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="J13" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="K13" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="L13" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="M13" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="N13" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>464</v>
+        <v>610</v>
       </c>
       <c r="O13" s="1">
         <v>800</v>
@@ -6255,21 +6325,21 @@
         <v>0.8</v>
       </c>
       <c r="Q13" s="4" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:18" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>14</v>
@@ -6280,39 +6350,39 @@
       </c>
       <c r="F14" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>84</v>
+        <v>53</v>
       </c>
       <c r="G14" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="H14" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="I14" s="14">
         <f t="shared" ca="1" si="0"/>
+        <v>57</v>
+      </c>
+      <c r="J14" s="14">
+        <f t="shared" ca="1" si="0"/>
         <v>80</v>
       </c>
-      <c r="J14" s="14">
+      <c r="K14" s="14">
+        <f t="shared" ca="1" si="0"/>
+        <v>97</v>
+      </c>
+      <c r="L14" s="14">
+        <f t="shared" ca="1" si="0"/>
+        <v>91</v>
+      </c>
+      <c r="M14" s="14">
         <f t="shared" ca="1" si="0"/>
         <v>49</v>
-      </c>
-      <c r="K14" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>87</v>
-      </c>
-      <c r="L14" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>94</v>
-      </c>
-      <c r="M14" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>44</v>
       </c>
       <c r="N14" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>588</v>
+        <v>526</v>
       </c>
       <c r="O14" s="1">
         <v>800</v>
@@ -6321,21 +6391,21 @@
         <v>0.89</v>
       </c>
       <c r="Q14" s="4" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:18" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>14</v>
@@ -6346,39 +6416,39 @@
       </c>
       <c r="F15" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="G15" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="H15" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="I15" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="J15" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="K15" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="L15" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="M15" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="N15" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>523</v>
+        <v>568</v>
       </c>
       <c r="O15" s="1">
         <v>800</v>
@@ -6387,24 +6457,24 @@
         <v>0.61</v>
       </c>
       <c r="Q15" s="4" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="R15" s="4" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:18" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E16" s="2" t="str">
         <f t="shared" si="1"/>
@@ -6412,39 +6482,39 @@
       </c>
       <c r="F16" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="G16" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="H16" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I16" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="J16" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="K16" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="L16" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M16" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>91</v>
+        <v>41</v>
       </c>
       <c r="N16" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>636</v>
+        <v>544</v>
       </c>
       <c r="O16" s="1">
         <v>800</v>
@@ -6453,24 +6523,24 @@
         <v>0.63</v>
       </c>
       <c r="Q16" s="4" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="R16" s="4" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:18" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E17" s="2" t="str">
         <f t="shared" si="1"/>
@@ -6478,39 +6548,39 @@
       </c>
       <c r="F17" s="14">
         <f t="shared" ca="1" si="2"/>
+        <v>62</v>
+      </c>
+      <c r="G17" s="14">
+        <f t="shared" ca="1" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="H17" s="14">
+        <f t="shared" ca="1" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="I17" s="14">
+        <f t="shared" ca="1" si="0"/>
         <v>56</v>
       </c>
-      <c r="G17" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>85</v>
-      </c>
-      <c r="H17" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>61</v>
-      </c>
-      <c r="I17" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>66</v>
-      </c>
       <c r="J17" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>47</v>
+        <v>88</v>
       </c>
       <c r="K17" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="L17" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>84</v>
+        <v>49</v>
       </c>
       <c r="M17" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="N17" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>523</v>
+        <v>482</v>
       </c>
       <c r="O17" s="1">
         <v>800</v>
@@ -6519,24 +6589,24 @@
         <v>0.48</v>
       </c>
       <c r="Q17" s="4" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="R17" s="4" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:18" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E18" s="2" t="str">
         <f t="shared" si="1"/>
@@ -6544,23 +6614,23 @@
       </c>
       <c r="F18" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="G18" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="H18" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="I18" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="J18" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="K18" s="14">
         <f t="shared" ca="1" si="0"/>
@@ -6568,15 +6638,15 @@
       </c>
       <c r="L18" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="M18" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="N18" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>522</v>
+        <v>533</v>
       </c>
       <c r="O18" s="1">
         <v>800</v>
@@ -6585,24 +6655,24 @@
         <v>0.59</v>
       </c>
       <c r="Q18" s="4" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="R18" s="4" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:18" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E19" s="2" t="str">
         <f t="shared" si="1"/>
@@ -6610,39 +6680,39 @@
       </c>
       <c r="F19" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G19" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="H19" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>91</v>
+        <v>44</v>
       </c>
       <c r="I19" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="J19" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="K19" s="14">
         <f t="shared" ca="1" si="0"/>
+        <v>61</v>
+      </c>
+      <c r="L19" s="14">
+        <f t="shared" ca="1" si="0"/>
         <v>67</v>
       </c>
-      <c r="L19" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>99</v>
-      </c>
       <c r="M19" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="N19" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>614</v>
+        <v>484</v>
       </c>
       <c r="O19" s="1">
         <v>800</v>
@@ -6651,24 +6721,24 @@
         <v>0.45</v>
       </c>
       <c r="Q19" s="4" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="R19" s="4" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20" spans="1:18" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E20" s="2" t="str">
         <f t="shared" si="1"/>
@@ -6676,39 +6746,39 @@
       </c>
       <c r="F20" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="G20" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H20" s="14">
         <f t="shared" ca="1" si="0"/>
+        <v>56</v>
+      </c>
+      <c r="I20" s="14">
+        <f t="shared" ca="1" si="0"/>
+        <v>77</v>
+      </c>
+      <c r="J20" s="14">
+        <f t="shared" ca="1" si="0"/>
         <v>58</v>
       </c>
-      <c r="I20" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>84</v>
-      </c>
-      <c r="J20" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>91</v>
-      </c>
       <c r="K20" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>92</v>
+        <v>50</v>
       </c>
       <c r="L20" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>85</v>
+        <v>53</v>
       </c>
       <c r="M20" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="N20" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>658</v>
+        <v>540</v>
       </c>
       <c r="O20" s="1">
         <v>800</v>
@@ -6717,24 +6787,24 @@
         <v>0.75</v>
       </c>
       <c r="Q20" s="4" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="R20" s="4" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:18" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E21" s="2" t="str">
         <f t="shared" si="1"/>
@@ -6742,39 +6812,39 @@
       </c>
       <c r="F21" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="G21" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="H21" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="I21" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>57</v>
+        <v>95</v>
       </c>
       <c r="J21" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>57</v>
+        <v>90</v>
       </c>
       <c r="K21" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>96</v>
+        <v>62</v>
       </c>
       <c r="L21" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="M21" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="N21" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>549</v>
+        <v>616</v>
       </c>
       <c r="O21" s="1">
         <v>800</v>
@@ -6783,24 +6853,24 @@
         <v>0.72</v>
       </c>
       <c r="Q21" s="4" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="R21" s="4" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:18" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E22" s="2" t="str">
         <f t="shared" si="1"/>
@@ -6808,39 +6878,39 @@
       </c>
       <c r="F22" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>52</v>
+        <v>100</v>
       </c>
       <c r="G22" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="H22" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I22" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="J22" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="K22" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="L22" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="M22" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="N22" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>543</v>
+        <v>756</v>
       </c>
       <c r="O22" s="1">
         <v>800</v>
@@ -6849,24 +6919,24 @@
         <v>0.68</v>
       </c>
       <c r="Q22" s="4" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="R22" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:18" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E23" s="2" t="str">
         <f t="shared" si="1"/>
@@ -6874,23 +6944,23 @@
       </c>
       <c r="F23" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G23" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="H23" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="I23" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="J23" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>49</v>
+        <v>83</v>
       </c>
       <c r="K23" s="14">
         <f t="shared" ca="1" si="0"/>
@@ -6898,15 +6968,15 @@
       </c>
       <c r="L23" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="M23" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="N23" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="O23" s="1">
         <v>800</v>
@@ -6915,24 +6985,24 @@
         <v>0.49</v>
       </c>
       <c r="Q23" s="4" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="R23" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:18" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E24" s="2" t="str">
         <f t="shared" si="1"/>
@@ -6940,39 +7010,39 @@
       </c>
       <c r="F24" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>47</v>
+        <v>86</v>
       </c>
       <c r="G24" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="H24" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="I24" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="J24" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>55</v>
+        <v>99</v>
       </c>
       <c r="K24" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="L24" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="M24" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="N24" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>572</v>
+        <v>579</v>
       </c>
       <c r="O24" s="1">
         <v>800</v>
@@ -6984,21 +7054,21 @@
         <v>15</v>
       </c>
       <c r="R24" s="4" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="25" spans="1:18" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E25" s="2" t="str">
         <f t="shared" si="1"/>
@@ -7006,39 +7076,39 @@
       </c>
       <c r="F25" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="G25" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="H25" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="I25" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="J25" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="K25" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="L25" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>43</v>
+        <v>99</v>
       </c>
       <c r="M25" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="N25" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="O25" s="1">
         <v>800</v>
@@ -7050,18 +7120,18 @@
         <v>15</v>
       </c>
       <c r="R25" s="4" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26" spans="1:18" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>14</v>
@@ -7072,39 +7142,39 @@
       </c>
       <c r="F26" s="14">
         <f t="shared" ca="1" si="2"/>
+        <v>49</v>
+      </c>
+      <c r="G26" s="14">
+        <f t="shared" ca="1" si="2"/>
+        <v>78</v>
+      </c>
+      <c r="H26" s="14">
+        <f t="shared" ca="1" si="2"/>
+        <v>96</v>
+      </c>
+      <c r="I26" s="14">
+        <f t="shared" ca="1" si="2"/>
+        <v>54</v>
+      </c>
+      <c r="J26" s="14">
+        <f t="shared" ca="1" si="2"/>
+        <v>88</v>
+      </c>
+      <c r="K26" s="14">
+        <f t="shared" ca="1" si="2"/>
+        <v>53</v>
+      </c>
+      <c r="L26" s="14">
+        <f t="shared" ca="1" si="2"/>
+        <v>52</v>
+      </c>
+      <c r="M26" s="14">
+        <f t="shared" ca="1" si="2"/>
         <v>89</v>
-      </c>
-      <c r="G26" s="14">
-        <f t="shared" ca="1" si="2"/>
-        <v>94</v>
-      </c>
-      <c r="H26" s="14">
-        <f t="shared" ca="1" si="2"/>
-        <v>44</v>
-      </c>
-      <c r="I26" s="14">
-        <f t="shared" ca="1" si="2"/>
-        <v>41</v>
-      </c>
-      <c r="J26" s="14">
-        <f t="shared" ca="1" si="2"/>
-        <v>54</v>
-      </c>
-      <c r="K26" s="14">
-        <f t="shared" ca="1" si="2"/>
-        <v>69</v>
-      </c>
-      <c r="L26" s="14">
-        <f t="shared" ca="1" si="2"/>
-        <v>83</v>
-      </c>
-      <c r="M26" s="14">
-        <f t="shared" ca="1" si="2"/>
-        <v>65</v>
       </c>
       <c r="N26" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>539</v>
+        <v>559</v>
       </c>
       <c r="O26" s="1">
         <v>800</v>
@@ -7116,18 +7186,18 @@
         <v>15</v>
       </c>
       <c r="R26" s="4" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27" spans="1:18" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>14</v>
@@ -7138,39 +7208,39 @@
       </c>
       <c r="F27" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="G27" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="H27" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I27" s="14">
         <f t="shared" ca="1" si="2"/>
+        <v>56</v>
+      </c>
+      <c r="J27" s="14">
+        <f t="shared" ca="1" si="2"/>
+        <v>48</v>
+      </c>
+      <c r="K27" s="14">
+        <f t="shared" ca="1" si="2"/>
+        <v>50</v>
+      </c>
+      <c r="L27" s="14">
+        <f t="shared" ca="1" si="2"/>
+        <v>79</v>
+      </c>
+      <c r="M27" s="14">
+        <f t="shared" ca="1" si="2"/>
         <v>64</v>
-      </c>
-      <c r="J27" s="14">
-        <f t="shared" ca="1" si="2"/>
-        <v>85</v>
-      </c>
-      <c r="K27" s="14">
-        <f t="shared" ca="1" si="2"/>
-        <v>58</v>
-      </c>
-      <c r="L27" s="14">
-        <f t="shared" ca="1" si="2"/>
-        <v>70</v>
-      </c>
-      <c r="M27" s="14">
-        <f t="shared" ca="1" si="2"/>
-        <v>55</v>
       </c>
       <c r="N27" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>510</v>
+        <v>519</v>
       </c>
       <c r="O27" s="1">
         <v>800</v>
@@ -7182,7 +7252,7 @@
         <v>15</v>
       </c>
       <c r="R27" s="4" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\python work\school_management_by_sumayya\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F30FD7D3-7FAF-4A51-B908-223B015F361D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A1861DA-C827-4C94-A26A-0A34AD3A1E88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1983,7 +1983,7 @@
     <col min="12" max="12" width="8" customWidth="1"/>
     <col min="13" max="13" width="8.5703125" customWidth="1"/>
     <col min="14" max="14" width="14.42578125" customWidth="1"/>
-    <col min="15" max="15" width="11.85546875" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" customWidth="1"/>
     <col min="16" max="16" width="13.140625" customWidth="1"/>
     <col min="17" max="18" width="11.85546875" customWidth="1"/>
   </cols>
@@ -2030,10 +2030,10 @@
         <v>18</v>
       </c>
       <c r="N7" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="O7" s="11" t="s">
         <v>9</v>
-      </c>
-      <c r="O7" s="11" t="s">
-        <v>10</v>
       </c>
       <c r="P7" s="11" t="s">
         <v>11</v>
@@ -4555,39 +4555,39 @@
       </c>
       <c r="F8" s="16">
         <f ca="1">RANDBETWEEN(40,100)</f>
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="G8" s="16">
         <f t="shared" ref="G8:M23" ca="1" si="0">RANDBETWEEN(40,100)</f>
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="H8" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="I8" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="J8" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="K8" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="L8" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="M8" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="N8" s="7">
         <f ca="1">SUM(F8:M8)</f>
-        <v>594</v>
+        <v>581</v>
       </c>
       <c r="O8" s="7">
         <v>800</v>
@@ -4621,39 +4621,39 @@
       </c>
       <c r="F9" s="14">
         <f t="shared" ref="F9:M27" ca="1" si="2">RANDBETWEEN(40,100)</f>
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="G9" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="H9" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="I9" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="J9" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="K9" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="L9" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="M9" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="N9" s="1">
         <f t="shared" ref="N9:N27" ca="1" si="3">SUM(F9:M9)</f>
-        <v>519</v>
+        <v>596</v>
       </c>
       <c r="O9" s="1">
         <v>800</v>
@@ -4687,39 +4687,39 @@
       </c>
       <c r="F10" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G10" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="H10" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="I10" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="J10" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="K10" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="L10" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="M10" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N10" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="O10" s="1">
         <v>800</v>
@@ -4753,39 +4753,39 @@
       </c>
       <c r="F11" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="G11" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="H11" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="I11" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="J11" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>50</v>
+        <v>93</v>
       </c>
       <c r="K11" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="L11" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="M11" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="N11" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>492</v>
+        <v>631</v>
       </c>
       <c r="O11" s="1">
         <v>800</v>
@@ -4819,31 +4819,31 @@
       </c>
       <c r="F12" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G12" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="H12" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="I12" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>88</v>
+        <v>42</v>
       </c>
       <c r="J12" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="K12" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="L12" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="M12" s="14">
         <f t="shared" ca="1" si="0"/>
@@ -4851,7 +4851,7 @@
       </c>
       <c r="N12" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>580</v>
+        <v>513</v>
       </c>
       <c r="O12" s="1">
         <v>800</v>
@@ -4885,39 +4885,39 @@
       </c>
       <c r="F13" s="14">
         <f t="shared" ca="1" si="2"/>
+        <v>48</v>
+      </c>
+      <c r="G13" s="14">
+        <f t="shared" ca="1" si="0"/>
+        <v>81</v>
+      </c>
+      <c r="H13" s="14">
+        <f t="shared" ca="1" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="I13" s="14">
+        <f t="shared" ca="1" si="0"/>
         <v>66</v>
       </c>
-      <c r="G13" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>58</v>
-      </c>
-      <c r="H13" s="14">
+      <c r="J13" s="14">
+        <f t="shared" ca="1" si="0"/>
+        <v>68</v>
+      </c>
+      <c r="K13" s="14">
+        <f t="shared" ca="1" si="0"/>
+        <v>68</v>
+      </c>
+      <c r="L13" s="14">
+        <f t="shared" ca="1" si="0"/>
+        <v>94</v>
+      </c>
+      <c r="M13" s="14">
         <f t="shared" ca="1" si="0"/>
         <v>93</v>
-      </c>
-      <c r="I13" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>43</v>
-      </c>
-      <c r="J13" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>47</v>
-      </c>
-      <c r="K13" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>40</v>
-      </c>
-      <c r="L13" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>58</v>
-      </c>
-      <c r="M13" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>71</v>
       </c>
       <c r="N13" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>476</v>
+        <v>581</v>
       </c>
       <c r="O13" s="1">
         <v>800</v>
@@ -4951,39 +4951,39 @@
       </c>
       <c r="F14" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="G14" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="H14" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="I14" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="J14" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="K14" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="L14" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="M14" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="N14" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="O14" s="1">
         <v>800</v>
@@ -5017,39 +5017,39 @@
       </c>
       <c r="F15" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="G15" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="H15" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="I15" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="J15" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="K15" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L15" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M15" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="N15" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="O15" s="1">
         <v>800</v>
@@ -5083,39 +5083,39 @@
       </c>
       <c r="F16" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="G16" s="14">
         <f t="shared" ca="1" si="0"/>
+        <v>78</v>
+      </c>
+      <c r="H16" s="14">
+        <f t="shared" ca="1" si="0"/>
+        <v>99</v>
+      </c>
+      <c r="I16" s="14">
+        <f t="shared" ca="1" si="0"/>
+        <v>91</v>
+      </c>
+      <c r="J16" s="14">
+        <f t="shared" ca="1" si="0"/>
         <v>97</v>
       </c>
-      <c r="H16" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>72</v>
-      </c>
-      <c r="I16" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>47</v>
-      </c>
-      <c r="J16" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>97</v>
-      </c>
       <c r="K16" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="L16" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>97</v>
+        <v>45</v>
       </c>
       <c r="M16" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="N16" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>603</v>
+        <v>544</v>
       </c>
       <c r="O16" s="1">
         <v>800</v>
@@ -5149,39 +5149,39 @@
       </c>
       <c r="F17" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="G17" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="H17" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="I17" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="J17" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="K17" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="L17" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="M17" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="N17" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>484</v>
+        <v>578</v>
       </c>
       <c r="O17" s="1">
         <v>800</v>
@@ -5215,39 +5215,39 @@
       </c>
       <c r="F18" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="G18" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="H18" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="I18" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>93</v>
+        <v>60</v>
       </c>
       <c r="J18" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>63</v>
+        <v>90</v>
       </c>
       <c r="K18" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="L18" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>61</v>
+        <v>100</v>
       </c>
       <c r="M18" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="N18" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>554</v>
+        <v>632</v>
       </c>
       <c r="O18" s="1">
         <v>800</v>
@@ -5281,39 +5281,39 @@
       </c>
       <c r="F19" s="14">
         <f t="shared" ca="1" si="2"/>
+        <v>97</v>
+      </c>
+      <c r="G19" s="14">
+        <f t="shared" ca="1" si="0"/>
+        <v>96</v>
+      </c>
+      <c r="H19" s="14">
+        <f t="shared" ca="1" si="0"/>
+        <v>66</v>
+      </c>
+      <c r="I19" s="14">
+        <f t="shared" ca="1" si="0"/>
+        <v>51</v>
+      </c>
+      <c r="J19" s="14">
+        <f t="shared" ca="1" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="K19" s="14">
+        <f t="shared" ca="1" si="0"/>
         <v>76</v>
       </c>
-      <c r="G19" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>65</v>
-      </c>
-      <c r="H19" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>96</v>
-      </c>
-      <c r="I19" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>97</v>
-      </c>
-      <c r="J19" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>78</v>
-      </c>
-      <c r="K19" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>52</v>
-      </c>
       <c r="L19" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="M19" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="N19" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>610</v>
+        <v>579</v>
       </c>
       <c r="O19" s="1">
         <v>800</v>
@@ -5347,39 +5347,39 @@
       </c>
       <c r="F20" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G20" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>99</v>
+        <v>42</v>
       </c>
       <c r="H20" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="I20" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="J20" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="K20" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="L20" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="M20" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N20" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>614</v>
+        <v>565</v>
       </c>
       <c r="O20" s="1">
         <v>800</v>
@@ -5413,39 +5413,39 @@
       </c>
       <c r="F21" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G21" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="H21" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="I21" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J21" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="K21" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="L21" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>41</v>
+        <v>81</v>
       </c>
       <c r="M21" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="N21" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>523</v>
+        <v>533</v>
       </c>
       <c r="O21" s="1">
         <v>800</v>
@@ -5479,39 +5479,39 @@
       </c>
       <c r="F22" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="G22" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="H22" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="I22" s="14">
         <f t="shared" ca="1" si="0"/>
+        <v>54</v>
+      </c>
+      <c r="J22" s="14">
+        <f t="shared" ca="1" si="0"/>
+        <v>89</v>
+      </c>
+      <c r="K22" s="14">
+        <f t="shared" ca="1" si="0"/>
+        <v>84</v>
+      </c>
+      <c r="L22" s="14">
+        <f t="shared" ca="1" si="0"/>
+        <v>53</v>
+      </c>
+      <c r="M22" s="14">
+        <f t="shared" ca="1" si="0"/>
         <v>68</v>
-      </c>
-      <c r="J22" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>76</v>
-      </c>
-      <c r="K22" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>90</v>
-      </c>
-      <c r="L22" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>54</v>
-      </c>
-      <c r="M22" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>91</v>
       </c>
       <c r="N22" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>588</v>
+        <v>562</v>
       </c>
       <c r="O22" s="1">
         <v>800</v>
@@ -5545,39 +5545,39 @@
       </c>
       <c r="F23" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="G23" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="H23" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="I23" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="J23" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="K23" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="L23" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="M23" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="N23" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>530</v>
+        <v>614</v>
       </c>
       <c r="O23" s="1">
         <v>800</v>
@@ -5611,39 +5611,39 @@
       </c>
       <c r="F24" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="G24" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="H24" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="I24" s="14">
         <f t="shared" ca="1" si="2"/>
+        <v>85</v>
+      </c>
+      <c r="J24" s="14">
+        <f t="shared" ca="1" si="2"/>
+        <v>85</v>
+      </c>
+      <c r="K24" s="14">
+        <f t="shared" ca="1" si="2"/>
+        <v>69</v>
+      </c>
+      <c r="L24" s="14">
+        <f t="shared" ca="1" si="2"/>
         <v>40</v>
       </c>
-      <c r="J24" s="14">
-        <f t="shared" ca="1" si="2"/>
-        <v>78</v>
-      </c>
-      <c r="K24" s="14">
-        <f t="shared" ca="1" si="2"/>
-        <v>74</v>
-      </c>
-      <c r="L24" s="14">
-        <f t="shared" ca="1" si="2"/>
-        <v>89</v>
-      </c>
       <c r="M24" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="N24" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>543</v>
+        <v>614</v>
       </c>
       <c r="O24" s="1">
         <v>800</v>
@@ -5677,39 +5677,39 @@
       </c>
       <c r="F25" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G25" s="14">
         <f t="shared" ca="1" si="2"/>
+        <v>48</v>
+      </c>
+      <c r="H25" s="14">
+        <f t="shared" ca="1" si="2"/>
+        <v>96</v>
+      </c>
+      <c r="I25" s="14">
+        <f t="shared" ca="1" si="2"/>
+        <v>82</v>
+      </c>
+      <c r="J25" s="14">
+        <f t="shared" ca="1" si="2"/>
         <v>71</v>
       </c>
-      <c r="H25" s="14">
-        <f t="shared" ca="1" si="2"/>
-        <v>54</v>
-      </c>
-      <c r="I25" s="14">
-        <f t="shared" ca="1" si="2"/>
-        <v>47</v>
-      </c>
-      <c r="J25" s="14">
-        <f t="shared" ca="1" si="2"/>
-        <v>47</v>
-      </c>
       <c r="K25" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="L25" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="M25" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>44</v>
+        <v>96</v>
       </c>
       <c r="N25" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>441</v>
+        <v>630</v>
       </c>
       <c r="O25" s="1">
         <v>800</v>
@@ -5743,39 +5743,39 @@
       </c>
       <c r="F26" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>94</v>
+        <v>53</v>
       </c>
       <c r="G26" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="H26" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I26" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="J26" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="K26" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="L26" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="M26" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="N26" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="O26" s="1">
         <v>800</v>
@@ -5809,39 +5809,39 @@
       </c>
       <c r="F27" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G27" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>42</v>
+        <v>99</v>
       </c>
       <c r="H27" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="I27" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J27" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="K27" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="L27" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="M27" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="N27" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>496</v>
+        <v>591</v>
       </c>
       <c r="O27" s="1">
         <v>800</v>
@@ -5954,39 +5954,39 @@
       </c>
       <c r="F8" s="14">
         <f ca="1">RANDBETWEEN(40,100)</f>
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="G8" s="14">
         <f t="shared" ref="G8:M23" ca="1" si="0">RANDBETWEEN(40,100)</f>
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="H8" s="14">
         <f t="shared" ca="1" si="0"/>
+        <v>54</v>
+      </c>
+      <c r="I8" s="14">
+        <f t="shared" ca="1" si="0"/>
+        <v>88</v>
+      </c>
+      <c r="J8" s="14">
+        <f t="shared" ca="1" si="0"/>
+        <v>86</v>
+      </c>
+      <c r="K8" s="14">
+        <f t="shared" ca="1" si="0"/>
         <v>77</v>
       </c>
-      <c r="I8" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>61</v>
-      </c>
-      <c r="J8" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>87</v>
-      </c>
-      <c r="K8" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>46</v>
-      </c>
       <c r="L8" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="M8" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="N8" s="1">
         <f ca="1">SUM(F8:M8)</f>
-        <v>515</v>
+        <v>649</v>
       </c>
       <c r="O8" s="1">
         <v>800</v>
@@ -6020,39 +6020,39 @@
       </c>
       <c r="F9" s="14">
         <f t="shared" ref="F9:M27" ca="1" si="2">RANDBETWEEN(40,100)</f>
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="G9" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H9" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="I9" s="14">
         <f t="shared" ca="1" si="0"/>
+        <v>81</v>
+      </c>
+      <c r="J9" s="14">
+        <f t="shared" ca="1" si="0"/>
+        <v>91</v>
+      </c>
+      <c r="K9" s="14">
+        <f t="shared" ca="1" si="0"/>
+        <v>93</v>
+      </c>
+      <c r="L9" s="14">
+        <f t="shared" ca="1" si="0"/>
+        <v>49</v>
+      </c>
+      <c r="M9" s="14">
+        <f t="shared" ca="1" si="0"/>
         <v>51</v>
-      </c>
-      <c r="J9" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>80</v>
-      </c>
-      <c r="K9" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>64</v>
-      </c>
-      <c r="L9" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>77</v>
-      </c>
-      <c r="M9" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>47</v>
       </c>
       <c r="N9" s="1">
         <f t="shared" ref="N9:N27" ca="1" si="3">SUM(F9:M9)</f>
-        <v>561</v>
+        <v>620</v>
       </c>
       <c r="O9" s="1">
         <v>800</v>
@@ -6086,39 +6086,39 @@
       </c>
       <c r="F10" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G10" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="H10" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="I10" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>55</v>
+        <v>99</v>
       </c>
       <c r="J10" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="K10" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="L10" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>93</v>
+        <v>51</v>
       </c>
       <c r="M10" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="N10" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>568</v>
+        <v>637</v>
       </c>
       <c r="O10" s="1">
         <v>800</v>
@@ -6152,39 +6152,39 @@
       </c>
       <c r="F11" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="G11" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="H11" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="I11" s="14">
         <f t="shared" ca="1" si="0"/>
+        <v>67</v>
+      </c>
+      <c r="J11" s="14">
+        <f t="shared" ca="1" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="K11" s="14">
+        <f t="shared" ca="1" si="0"/>
+        <v>82</v>
+      </c>
+      <c r="L11" s="14">
+        <f t="shared" ca="1" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="M11" s="14">
+        <f t="shared" ca="1" si="0"/>
         <v>56</v>
-      </c>
-      <c r="J11" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>84</v>
-      </c>
-      <c r="K11" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>59</v>
-      </c>
-      <c r="L11" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>95</v>
-      </c>
-      <c r="M11" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>62</v>
       </c>
       <c r="N11" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>618</v>
+        <v>557</v>
       </c>
       <c r="O11" s="1">
         <v>800</v>
@@ -6218,39 +6218,39 @@
       </c>
       <c r="F12" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>89</v>
+        <v>66</v>
       </c>
       <c r="G12" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="H12" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="I12" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="J12" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="K12" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="L12" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="M12" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N12" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>599</v>
+        <v>623</v>
       </c>
       <c r="O12" s="1">
         <v>800</v>
@@ -6284,39 +6284,39 @@
       </c>
       <c r="F13" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="G13" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>99</v>
+        <v>62</v>
       </c>
       <c r="H13" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I13" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="J13" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="K13" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="L13" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="M13" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N13" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>610</v>
+        <v>581</v>
       </c>
       <c r="O13" s="1">
         <v>800</v>
@@ -6350,39 +6350,39 @@
       </c>
       <c r="F14" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G14" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="H14" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="I14" s="14">
         <f t="shared" ca="1" si="0"/>
+        <v>92</v>
+      </c>
+      <c r="J14" s="14">
+        <f t="shared" ca="1" si="0"/>
+        <v>75</v>
+      </c>
+      <c r="K14" s="14">
+        <f t="shared" ca="1" si="0"/>
+        <v>59</v>
+      </c>
+      <c r="L14" s="14">
+        <f t="shared" ca="1" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="M14" s="14">
+        <f t="shared" ca="1" si="0"/>
         <v>57</v>
-      </c>
-      <c r="J14" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>80</v>
-      </c>
-      <c r="K14" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>97</v>
-      </c>
-      <c r="L14" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>91</v>
-      </c>
-      <c r="M14" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>49</v>
       </c>
       <c r="N14" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>526</v>
+        <v>513</v>
       </c>
       <c r="O14" s="1">
         <v>800</v>
@@ -6416,39 +6416,39 @@
       </c>
       <c r="F15" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="G15" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="H15" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="I15" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="J15" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="K15" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="L15" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="M15" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="N15" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>568</v>
+        <v>605</v>
       </c>
       <c r="O15" s="1">
         <v>800</v>
@@ -6482,39 +6482,39 @@
       </c>
       <c r="F16" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="G16" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="H16" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="I16" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="J16" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>98</v>
+        <v>50</v>
       </c>
       <c r="K16" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="L16" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M16" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="N16" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>544</v>
+        <v>573</v>
       </c>
       <c r="O16" s="1">
         <v>800</v>
@@ -6548,39 +6548,39 @@
       </c>
       <c r="F17" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="G17" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="H17" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I17" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="J17" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="K17" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="L17" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="M17" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="N17" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>482</v>
+        <v>637</v>
       </c>
       <c r="O17" s="1">
         <v>800</v>
@@ -6614,39 +6614,39 @@
       </c>
       <c r="F18" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="G18" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H18" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="I18" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="J18" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="K18" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="L18" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="M18" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="N18" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>533</v>
+        <v>609</v>
       </c>
       <c r="O18" s="1">
         <v>800</v>
@@ -6680,39 +6680,39 @@
       </c>
       <c r="F19" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="G19" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="H19" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>44</v>
+        <v>91</v>
       </c>
       <c r="I19" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="J19" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="K19" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="L19" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="M19" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>52</v>
+        <v>98</v>
       </c>
       <c r="N19" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>484</v>
+        <v>606</v>
       </c>
       <c r="O19" s="1">
         <v>800</v>
@@ -6746,39 +6746,39 @@
       </c>
       <c r="F20" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="G20" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H20" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="I20" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="J20" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K20" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="L20" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="M20" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="N20" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>540</v>
+        <v>564</v>
       </c>
       <c r="O20" s="1">
         <v>800</v>
@@ -6812,39 +6812,39 @@
       </c>
       <c r="F21" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="G21" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="H21" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="I21" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="J21" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="K21" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="L21" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="M21" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="N21" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="O21" s="1">
         <v>800</v>
@@ -6878,39 +6878,39 @@
       </c>
       <c r="F22" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="G22" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="H22" s="14">
         <f t="shared" ca="1" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="I22" s="14">
+        <f t="shared" ca="1" si="0"/>
+        <v>88</v>
+      </c>
+      <c r="J22" s="14">
+        <f t="shared" ca="1" si="0"/>
         <v>98</v>
       </c>
-      <c r="I22" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>82</v>
-      </c>
-      <c r="J22" s="14">
-        <f t="shared" ca="1" si="0"/>
-        <v>98</v>
-      </c>
       <c r="K22" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="L22" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="M22" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N22" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>756</v>
+        <v>592</v>
       </c>
       <c r="O22" s="1">
         <v>800</v>
@@ -6944,39 +6944,39 @@
       </c>
       <c r="F23" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="G23" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>94</v>
+        <v>41</v>
       </c>
       <c r="H23" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="I23" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="J23" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K23" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>51</v>
+        <v>92</v>
       </c>
       <c r="L23" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="M23" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>59</v>
+        <v>92</v>
       </c>
       <c r="N23" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>606</v>
+        <v>515</v>
       </c>
       <c r="O23" s="1">
         <v>800</v>
@@ -7010,23 +7010,23 @@
       </c>
       <c r="F24" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="G24" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="H24" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="I24" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>77</v>
+        <v>43</v>
       </c>
       <c r="J24" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="K24" s="14">
         <f t="shared" ca="1" si="2"/>
@@ -7038,11 +7038,11 @@
       </c>
       <c r="M24" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="N24" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>579</v>
+        <v>543</v>
       </c>
       <c r="O24" s="1">
         <v>800</v>
@@ -7076,39 +7076,39 @@
       </c>
       <c r="F25" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G25" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="H25" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="I25" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="J25" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="K25" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="L25" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="M25" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="N25" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>565</v>
+        <v>545</v>
       </c>
       <c r="O25" s="1">
         <v>800</v>
@@ -7142,7 +7142,7 @@
       </c>
       <c r="F26" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="G26" s="14">
         <f t="shared" ca="1" si="2"/>
@@ -7150,31 +7150,31 @@
       </c>
       <c r="H26" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>96</v>
+        <v>57</v>
       </c>
       <c r="I26" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="J26" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="K26" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="L26" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="M26" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>89</v>
+        <v>43</v>
       </c>
       <c r="N26" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>559</v>
+        <v>509</v>
       </c>
       <c r="O26" s="1">
         <v>800</v>
@@ -7208,39 +7208,39 @@
       </c>
       <c r="F27" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G27" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="H27" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="I27" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="J27" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>48</v>
+        <v>82</v>
       </c>
       <c r="K27" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L27" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="M27" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="N27" s="1">
         <f t="shared" ca="1" si="3"/>
-        <v>519</v>
+        <v>579</v>
       </c>
       <c r="O27" s="1">
         <v>800</v>
